--- a/Table S9.xlsx
+++ b/Table S9.xlsx
@@ -1,20 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\2024\Mestrado 2024-2025\Projeto e artigos\Resultados análises\Artigo Priscilla\Artigo\CORREÇÃO REVIEWER\Arquivos revisados\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="20505" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="492" windowWidth="20508" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Table S8" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -260,61 +255,10 @@
     <t>Hydrophobicity</t>
   </si>
   <si>
-    <t>11,88±2,98</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
-    <t>6,81±3,25</t>
-  </si>
-  <si>
-    <t>14,56±2,16</t>
-  </si>
-  <si>
-    <t>3,64±1,89</t>
-  </si>
-  <si>
-    <t>8,18±3,57</t>
-  </si>
-  <si>
-    <t>2,32±2,08</t>
-  </si>
-  <si>
-    <t>21,76±0,99</t>
-  </si>
-  <si>
-    <t>4,66±1,56</t>
-  </si>
-  <si>
-    <t>9,21±1,70</t>
-  </si>
-  <si>
-    <t>3,19±2,45</t>
-  </si>
-  <si>
-    <t>37,54±2,18</t>
-  </si>
-  <si>
     <t>M</t>
-  </si>
-  <si>
-    <t>6,86±2,89</t>
-  </si>
-  <si>
-    <t>4,60±8,42</t>
-  </si>
-  <si>
-    <t>6,84±7,51</t>
-  </si>
-  <si>
-    <t>6,37±3,97</t>
-  </si>
-  <si>
-    <t>2,49±2,06</t>
-  </si>
-  <si>
-    <t>1,08±0,94</t>
   </si>
   <si>
     <t>Classification*</t>
@@ -419,12 +363,63 @@
   <si>
     <t>Table S9. Adhesion properties of the 25 lactic acid bacteria strains (self-aggregation, hydrophobicity, and biofilm formation capacity).</t>
   </si>
+  <si>
+    <t>11.88±2.98</t>
+  </si>
+  <si>
+    <t>6.81±3.25</t>
+  </si>
+  <si>
+    <t>14.56±2.16</t>
+  </si>
+  <si>
+    <t>3.64±1.89</t>
+  </si>
+  <si>
+    <t>8.18±3.57</t>
+  </si>
+  <si>
+    <t>2.32±2.08</t>
+  </si>
+  <si>
+    <t>21.76±0.99</t>
+  </si>
+  <si>
+    <t>4.66±1.56</t>
+  </si>
+  <si>
+    <t>9.21±1.70</t>
+  </si>
+  <si>
+    <t>3.19±2.45</t>
+  </si>
+  <si>
+    <t>37.54±2.18</t>
+  </si>
+  <si>
+    <t>6.86±2.89</t>
+  </si>
+  <si>
+    <t>4.60±8.42</t>
+  </si>
+  <si>
+    <t>6.84±7.51</t>
+  </si>
+  <si>
+    <t>6.37±3.97</t>
+  </si>
+  <si>
+    <t>2.49±2.06</t>
+  </si>
+  <si>
+    <t>1.08±0.94</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -488,6 +483,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -684,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -732,13 +733,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1037,7 +1041,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1046,52 +1050,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-    </row>
-    <row r="2" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="A1" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="20" t="s">
+      <c r="B2" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="21"/>
+      <c r="F2" s="22"/>
       <c r="G2" s="12" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="26"/>
+    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.4">
+      <c r="A3" s="27"/>
       <c r="B3" s="9" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>1</v>
@@ -1100,13 +1104,13 @@
         <v>77</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
@@ -1114,22 +1118,22 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>5</v>
       </c>
@@ -1137,22 +1141,22 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>8</v>
       </c>
@@ -1160,22 +1164,22 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="19">
         <v>0</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>11</v>
       </c>
@@ -1183,22 +1187,22 @@
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="19">
         <v>0</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>14</v>
       </c>
@@ -1206,22 +1210,22 @@
         <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>17</v>
       </c>
@@ -1229,22 +1233,22 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="19">
         <v>0</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>20</v>
       </c>
@@ -1252,22 +1256,22 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>23</v>
       </c>
@@ -1275,22 +1279,22 @@
         <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -1298,22 +1302,22 @@
         <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -1321,22 +1325,22 @@
         <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="19">
         <v>0</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>32</v>
       </c>
@@ -1344,22 +1348,22 @@
         <v>33</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="19">
         <v>0</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>35</v>
       </c>
@@ -1367,22 +1371,22 @@
         <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="19">
         <v>0</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>38</v>
       </c>
@@ -1390,22 +1394,22 @@
         <v>39</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="19">
         <v>0</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>41</v>
       </c>
@@ -1413,22 +1417,22 @@
         <v>42</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>43</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>44</v>
       </c>
@@ -1436,22 +1440,22 @@
         <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>46</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>47</v>
       </c>
@@ -1459,22 +1463,22 @@
         <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>49</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>50</v>
       </c>
@@ -1482,22 +1486,22 @@
         <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>53</v>
       </c>
@@ -1505,22 +1509,22 @@
         <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>55</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>56</v>
       </c>
@@ -1528,22 +1532,22 @@
         <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>58</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>59</v>
       </c>
@@ -1551,22 +1555,22 @@
         <v>60</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>61</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>62</v>
       </c>
@@ -1574,22 +1578,22 @@
         <v>63</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>64</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>65</v>
       </c>
@@ -1597,22 +1601,22 @@
         <v>66</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>68</v>
       </c>
@@ -1620,22 +1624,22 @@
         <v>69</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>70</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>71</v>
       </c>
@@ -1643,22 +1647,22 @@
         <v>72</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>73</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>74</v>
       </c>
@@ -1666,31 +1670,31 @@
         <v>75</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="D28" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="20">
         <v>0</v>
       </c>
-      <c r="F28" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>116</v>
+      <c r="F28" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
+      <c r="A29" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="5">
